--- a/analysis docs/metabolic_features.xlsx
+++ b/analysis docs/metabolic_features.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaveh/PhD/Projects/Cell Fate/CellFate/analysis/Fate Analysis Docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaveh/PhD/Projects/FateFormer/FateFormerRepo/analysis docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD988A1D-2C54-1E44-A17E-8A2A436AA609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957262BB-3935-E343-89F1-307B658CFF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" xr2:uid="{9176B6A6-D9CA-4D4F-B897-E429559686BF}"/>
   </bookViews>
@@ -2506,7 +2506,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7384566E-3982-B64A-ABEB-05C6E42B3040}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2586,7 +2585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3012,7 +3011,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3083,7 +3082,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3154,7 +3153,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3225,7 +3224,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3367,7 +3366,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3438,7 +3437,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3580,7 +3579,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3651,7 +3650,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3722,7 +3721,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3793,7 +3792,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3864,7 +3863,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4077,7 +4076,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4148,7 +4147,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4290,7 +4289,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4361,7 +4360,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4432,7 +4431,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4645,7 +4644,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4716,7 +4715,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4858,7 +4857,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4929,7 +4928,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5000,7 +4999,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5071,7 +5070,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5142,7 +5141,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5213,7 +5212,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5284,7 +5283,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5355,7 +5354,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5426,7 +5425,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5497,7 +5496,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5568,7 +5567,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5639,7 +5638,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5710,7 +5709,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5781,7 +5780,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5852,7 +5851,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5923,7 +5922,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5994,7 +5993,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6065,7 +6064,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6136,7 +6135,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6207,7 +6206,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6349,7 +6348,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6491,7 +6490,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6562,7 +6561,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6704,7 +6703,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6775,7 +6774,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6846,7 +6845,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6917,7 +6916,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6988,7 +6987,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7059,7 +7058,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7130,7 +7129,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7201,7 +7200,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7272,7 +7271,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7343,7 +7342,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7414,7 +7413,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7485,7 +7484,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7556,7 +7555,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7627,7 +7626,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7698,7 +7697,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7769,7 +7768,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7840,7 +7839,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7911,7 +7910,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7982,7 +7981,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -8053,7 +8052,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -8124,7 +8123,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -8195,7 +8194,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -8266,7 +8265,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -8337,7 +8336,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -8408,7 +8407,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -8479,7 +8478,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -8550,7 +8549,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -8621,7 +8620,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -8692,7 +8691,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -8763,7 +8762,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8834,7 +8833,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8976,7 +8975,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9118,7 +9117,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9189,7 +9188,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9260,7 +9259,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9331,7 +9330,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9402,7 +9401,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9473,7 +9472,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9544,7 +9543,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9615,7 +9614,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9686,7 +9685,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -9757,7 +9756,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -9828,7 +9827,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -9970,7 +9969,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10041,7 +10040,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10112,7 +10111,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10183,7 +10182,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10254,7 +10253,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10325,7 +10324,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10396,7 +10395,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10467,7 +10466,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10609,7 +10608,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="115" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10680,7 +10679,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="116" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10751,7 +10750,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10822,7 +10821,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10893,7 +10892,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10964,7 +10963,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -11035,7 +11034,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -11106,7 +11105,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -11177,7 +11176,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -11248,7 +11247,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -11319,7 +11318,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -11390,7 +11389,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -11461,7 +11460,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -11532,7 +11531,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -11603,7 +11602,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -11674,7 +11673,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -11745,7 +11744,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -11816,7 +11815,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -11887,7 +11886,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -11958,7 +11957,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -12029,7 +12028,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -12100,7 +12099,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -12171,7 +12170,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -12242,7 +12241,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -12313,7 +12312,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -12384,7 +12383,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -12455,7 +12454,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -12526,7 +12525,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -12597,7 +12596,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -12668,7 +12667,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -12739,7 +12738,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -12810,7 +12809,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -12881,7 +12880,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -12952,7 +12951,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -13023,7 +13022,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -13165,7 +13164,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -13236,7 +13235,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -13378,7 +13377,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -13449,7 +13448,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -13520,7 +13519,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -13591,7 +13590,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
@@ -13733,7 +13732,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -13804,7 +13803,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -13875,7 +13874,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
@@ -13946,7 +13945,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -14017,7 +14016,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -14088,7 +14087,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -14159,7 +14158,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -14230,7 +14229,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
@@ -14301,7 +14300,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -14372,7 +14371,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -14443,7 +14442,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -14515,13 +14514,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:W169" xr:uid="{7384566E-3982-B64A-ABEB-05C6E42B3040}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="N-linked glycan synthesis"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:W169" xr:uid="{7384566E-3982-B64A-ABEB-05C6E42B3040}"/>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>$E$8</formula>
